--- a/data/bible.xlsx
+++ b/data/bible.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="91">
   <si>
     <t>Bible Reading Tracker</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>1-3</t>
+  </si>
+  <si>
+    <t>4-6</t>
   </si>
   <si>
     <t>Books Progress</t>
@@ -714,7 +717,7 @@
       </c>
       <c r="D3" s="3">
         <f>'Books Progress'!F1</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -723,7 +726,7 @@
       </c>
       <c r="D4" s="3">
         <f>'Books Progress'!F2</f>
-        <v>0.007569386039</v>
+        <v>0.01009251472</v>
       </c>
     </row>
     <row r="5">
@@ -741,7 +744,7 @@
       </c>
       <c r="D6" s="3">
         <f>'Books Progress'!F4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1888,13 +1891,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
+      <c r="A8" s="8">
+        <v>46321.0</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="D8" s="13"/>
       <c r="E8" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7639,17 +7648,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="18">
         <f>SUM(D7:D72)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="F2" s="19">
         <f>F1/D5</f>
-        <v>0.007569386039</v>
+        <v>0.01009251472</v>
       </c>
     </row>
     <row r="3">
@@ -7661,12 +7670,12 @@
     <row r="4">
       <c r="F4" s="19">
         <f>COUNTA('Daily Log'!A2:A399)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="20">
         <v>1189.0</v>
@@ -7677,24 +7686,24 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="22">
         <v>50.0</v>
@@ -7710,10 +7719,10 @@
     </row>
     <row r="8">
       <c r="A8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>26</v>
       </c>
       <c r="C8" s="22">
         <v>40.0</v>
@@ -7729,10 +7738,10 @@
     </row>
     <row r="9">
       <c r="A9" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="22">
         <v>27.0</v>
@@ -7748,10 +7757,10 @@
     </row>
     <row r="10">
       <c r="A10" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="22">
         <v>36.0</v>
@@ -7767,10 +7776,10 @@
     </row>
     <row r="11">
       <c r="A11" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="22">
         <v>34.0</v>
@@ -7786,10 +7795,10 @@
     </row>
     <row r="12">
       <c r="A12" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="22">
         <v>24.0</v>
@@ -7805,10 +7814,10 @@
     </row>
     <row r="13">
       <c r="A13" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="22">
         <v>21.0</v>
@@ -7824,10 +7833,10 @@
     </row>
     <row r="14">
       <c r="A14" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="22">
         <v>4.0</v>
@@ -7843,10 +7852,10 @@
     </row>
     <row r="15">
       <c r="A15" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" s="22">
         <v>31.0</v>
@@ -7862,10 +7871,10 @@
     </row>
     <row r="16">
       <c r="A16" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="22">
         <v>24.0</v>
@@ -7881,10 +7890,10 @@
     </row>
     <row r="17">
       <c r="A17" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" s="22">
         <v>22.0</v>
@@ -7900,10 +7909,10 @@
     </row>
     <row r="18">
       <c r="A18" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" s="22">
         <v>25.0</v>
@@ -7919,10 +7928,10 @@
     </row>
     <row r="19">
       <c r="A19" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="22">
         <v>29.0</v>
@@ -7938,10 +7947,10 @@
     </row>
     <row r="20">
       <c r="A20" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="22">
         <v>36.0</v>
@@ -7957,10 +7966,10 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="22">
         <v>10.0</v>
@@ -7976,10 +7985,10 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" s="22">
         <v>13.0</v>
@@ -7995,10 +8004,10 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" s="22">
         <v>10.0</v>
@@ -8014,10 +8023,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="22">
         <v>42.0</v>
@@ -8036,26 +8045,26 @@
         <v>17</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" s="22">
         <v>150.0</v>
       </c>
       <c r="D25" s="22">
         <f>SUMIFS('Daily Log'!$E$2:$E$399,'Daily Log'!$B$2:$B$399,A25)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" s="23">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" s="22">
         <v>31.0</v>
@@ -8071,10 +8080,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" s="22">
         <v>12.0</v>
@@ -8090,10 +8099,10 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" s="22">
         <v>8.0</v>
@@ -8109,10 +8118,10 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" s="22">
         <v>66.0</v>
@@ -8128,10 +8137,10 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" s="22">
         <v>52.0</v>
@@ -8147,10 +8156,10 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" s="22">
         <v>5.0</v>
@@ -8166,10 +8175,10 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="22">
         <v>48.0</v>
@@ -8185,10 +8194,10 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" s="22">
         <v>12.0</v>
@@ -8204,10 +8213,10 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" s="22">
         <v>14.0</v>
@@ -8223,10 +8232,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" s="22">
         <v>3.0</v>
@@ -8242,10 +8251,10 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" s="22">
         <v>9.0</v>
@@ -8261,10 +8270,10 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" s="22">
         <v>1.0</v>
@@ -8280,10 +8289,10 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" s="22">
         <v>4.0</v>
@@ -8299,10 +8308,10 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" s="22">
         <v>7.0</v>
@@ -8318,10 +8327,10 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" s="22">
         <v>3.0</v>
@@ -8337,10 +8346,10 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" s="22">
         <v>3.0</v>
@@ -8356,10 +8365,10 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" s="22">
         <v>3.0</v>
@@ -8375,10 +8384,10 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" s="22">
         <v>2.0</v>
@@ -8394,10 +8403,10 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" s="22">
         <v>14.0</v>
@@ -8413,10 +8422,10 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="22">
         <v>4.0</v>
@@ -8432,10 +8441,10 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" s="22">
         <v>28.0</v>
@@ -8451,10 +8460,10 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="22" t="s">
         <v>66</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>65</v>
       </c>
       <c r="C47" s="22">
         <v>16.0</v>
@@ -8470,10 +8479,10 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C48" s="22">
         <v>24.0</v>
@@ -8489,10 +8498,10 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C49" s="22">
         <v>21.0</v>
@@ -8508,10 +8517,10 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C50" s="22">
         <v>28.0</v>
@@ -8527,10 +8536,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C51" s="22">
         <v>16.0</v>
@@ -8546,10 +8555,10 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C52" s="22">
         <v>16.0</v>
@@ -8565,10 +8574,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C53" s="22">
         <v>13.0</v>
@@ -8584,10 +8593,10 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C54" s="22">
         <v>6.0</v>
@@ -8603,10 +8612,10 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C55" s="22">
         <v>6.0</v>
@@ -8622,10 +8631,10 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C56" s="22">
         <v>4.0</v>
@@ -8641,10 +8650,10 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C57" s="22">
         <v>4.0</v>
@@ -8660,10 +8669,10 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C58" s="22">
         <v>5.0</v>
@@ -8679,10 +8688,10 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C59" s="22">
         <v>3.0</v>
@@ -8698,10 +8707,10 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C60" s="22">
         <v>6.0</v>
@@ -8717,10 +8726,10 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C61" s="22">
         <v>4.0</v>
@@ -8736,10 +8745,10 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C62" s="22">
         <v>3.0</v>
@@ -8755,10 +8764,10 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C63" s="22">
         <v>1.0</v>
@@ -8774,10 +8783,10 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C64" s="22">
         <v>13.0</v>
@@ -8793,10 +8802,10 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C65" s="22">
         <v>5.0</v>
@@ -8815,7 +8824,7 @@
         <v>10</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C66" s="22">
         <v>5.0</v>
@@ -8834,7 +8843,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C67" s="22">
         <v>3.0</v>
@@ -8850,10 +8859,10 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C68" s="22">
         <v>5.0</v>
@@ -8869,10 +8878,10 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C69" s="22">
         <v>1.0</v>
@@ -8888,10 +8897,10 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C70" s="22">
         <v>1.0</v>
@@ -8907,10 +8916,10 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C71" s="22">
         <v>1.0</v>
@@ -8926,10 +8935,10 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C72" s="22">
         <v>22.0</v>
